--- a/docs/testing/tetomi-manual-test.xlsx
+++ b/docs/testing/tetomi-manual-test.xlsx
@@ -2327,15 +2327,19 @@
       </c>
       <c r="F32" s="49" t="inlineStr">
         <is>
-          <t>未実施</t>
+          <t>自動化済み</t>
         </is>
       </c>
       <c r="G32" s="54" t="inlineStr">
         <is>
-          <t>自動テストにできる見込み（スマホ幅で表示）。未着手</t>
-        </is>
-      </c>
-      <c r="H32" s="54" t="n"/>
+          <t>自動テスト T37（390px の画面で、候補日3件・場所・メッセージ・「確認へ進む」「購入希望を送る」まで押せる。横のはみ出しなし）</t>
+        </is>
+      </c>
+      <c r="H32" s="54" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="33.75" customHeight="1" s="29">
       <c r="A33" s="55" t="n">
@@ -2363,15 +2367,19 @@
       </c>
       <c r="F33" s="49" t="inlineStr">
         <is>
-          <t>未実施</t>
+          <t>自動化済み</t>
         </is>
       </c>
       <c r="G33" s="50" t="inlineStr">
         <is>
-          <t>自動テストにできる見込み（通信を切った状態で押す）。未着手</t>
-        </is>
-      </c>
-      <c r="H33" s="50" t="n"/>
+          <t>自動テスト T38（往復2.5秒の回線で3回たたいても購入希望は1件。押した直後にボタンが無効・「送信中…」）</t>
+        </is>
+      </c>
+      <c r="H33" s="50" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="33.75" customHeight="1" s="29">
       <c r="A34" s="56" t="n">
@@ -2644,7 +2652,7 @@
       </c>
       <c r="G40" s="50" t="inlineStr">
         <is>
-          <t>開発モードでは準備処理が2回走り、1回目の後片付けが2回目のカメラまで止めて画面が真っ黒になる（components/BarcodeScanner.tsx）。本番では起きない見込み。別ブランチで修正予定</t>
+          <t>修正済み（ブランチ fix/scanner-camera-dev-strictmode）。原因は2つ：読み取り画面の後片付けがカメラを止めていた／受け渡しQRの合言葉を2回発行してQRが無効になっていた。develop に入ったら npm run dev の画面で実際に読み取って確認する</t>
         </is>
       </c>
       <c r="H40" s="50" t="inlineStr">
@@ -2684,7 +2692,7 @@
       </c>
       <c r="G41" s="50" t="inlineStr">
         <is>
-          <t>「手入力をご利用ください」と出るが、決済のQRを手で入力する欄はどこにも無い（自動テスト T31 で発見）。文言を直すか手入力を作るか要判断</t>
+          <t>修正済み（ブランチ fix/scanner-camera-dev-strictmode）。受け渡しQRでは「ブラウザの設定でこのサイトのカメラを許可してから、もう一度お試しください。」に変更（ISBN の読み取りは手入力の欄があるので今までどおり）。develop に入ったら確認</t>
         </is>
       </c>
       <c r="H41" s="50" t="inlineStr">
